--- a/questions.xlsx
+++ b/questions.xlsx
@@ -403,16 +403,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -579,16 +569,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="50.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,53 +607,59 @@
         <v>Posted</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Which body formulates monetary policy in India?</v>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Consider the following statements regarding the 'AP-Green' initiative and forest data in Andhra Pradesh:
+1. At present, forest area covers 22.96% of the state's total geographical area (37.42 lakh hectares).
+2. AP-Green is set up as an autonomous body to bring all green-cover initiatives onto a single platform.
+3. Funding for AP-Green projects includes sources such as Carbon Finance, Green Bonds, District Mineral Fund, and NABARD.
+Which of the statements given above are correct?</v>
       </c>
       <c r="B2" t="str">
-        <v>NITI Aayog</v>
+        <v>1 and 2 only</v>
       </c>
       <c r="C2" t="str">
-        <v>Finance Ministry</v>
+        <v>2 and 3 only</v>
       </c>
       <c r="D2" t="str">
-        <v>RBI</v>
+        <v>1 and 3 only</v>
       </c>
       <c r="E2" t="str">
-        <v>SEBI</v>
+        <v>1, 2, and 3</v>
       </c>
       <c r="F2" t="str">
-        <v>C</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Reserve Bank of India (RBI) formulates monetary policy.</v>
+        <v>D</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">* Statement 1 is correct: Andhra Pradesh currently has 37.42 lakh hectares under forest cover, which is 22.96% of the state's geographical area.
+* Statement 2 is correct: 'AP-Green' is an autonomous entity designed to coordinate multi-departmental efforts on a unified platform to reach 50% green cover by 2047.
+* Statement 3 is correct: Resources will be mobilized via Carbon Finance, Green Bonds, DMF, and NABARD.</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>YES | 4/9/2026, 11:24:11 pm</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>What does GDP stand for?</v>
+        <v>Which body formulates monetary policy in India?</v>
       </c>
       <c r="B3" t="str">
-        <v>Gross Domestic Product</v>
+        <v>NITI Aayog</v>
       </c>
       <c r="C3" t="str">
-        <v>General Domestic Price</v>
+        <v>Finance Ministry</v>
       </c>
       <c r="D3" t="str">
-        <v>Gross Development Plan</v>
+        <v>RBI</v>
       </c>
       <c r="E3" t="str">
-        <v>General Development Product</v>
+        <v>SEBI</v>
       </c>
       <c r="F3" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="G3" t="str">
-        <v>GDP = Gross Domestic Product, total value of goods and services.</v>
+        <v>Reserve Bank of India (RBI) formulates monetary policy.</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -671,25 +667,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Which Five Year Plan is known as the Mahalanobis Plan?</v>
+        <v>What does GDP stand for?</v>
       </c>
       <c r="B4" t="str">
-        <v>First</v>
+        <v>Gross Domestic Product</v>
       </c>
       <c r="C4" t="str">
-        <v>Second</v>
+        <v>General Domestic Price</v>
       </c>
       <c r="D4" t="str">
-        <v>Third</v>
+        <v>Gross Development Plan</v>
       </c>
       <c r="E4" t="str">
-        <v>Fourth</v>
+        <v>General Development Product</v>
       </c>
       <c r="F4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G4" t="str">
-        <v>The Second Five Year Plan (1956-61) was the Mahalanobis Plan.</v>
+        <v>GDP = Gross Domestic Product, total value of goods and services.</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -697,25 +693,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>GST was introduced in India in which year?</v>
+        <v>Which Five Year Plan is known as the Mahalanobis Plan?</v>
       </c>
       <c r="B5" t="str">
-        <v>2015</v>
+        <v>First</v>
       </c>
       <c r="C5" t="str">
-        <v>2016</v>
+        <v>Second</v>
       </c>
       <c r="D5" t="str">
-        <v>2017</v>
+        <v>Third</v>
       </c>
       <c r="E5" t="str">
-        <v>2018</v>
+        <v>Fourth</v>
       </c>
       <c r="F5" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="G5" t="str">
-        <v>GST was implemented on July 1, 2017.</v>
+        <v>The Second Five Year Plan (1956-61) was the Mahalanobis Plan.</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -723,33 +719,59 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>GST was introduced in India in which year?</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2015</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2016</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2017</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2018</v>
+      </c>
+      <c r="F6" t="str">
+        <v>C</v>
+      </c>
+      <c r="G6" t="str">
+        <v>GST was implemented on July 1, 2017.</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>NABARD is associated with which sector?</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>Industrial</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C7" t="str">
         <v>Agricultural</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D7" t="str">
         <v>Service</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E7" t="str">
         <v>Mining</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F7" t="str">
         <v>B</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G7" t="str">
         <v>NABARD focuses on agriculture and rural development.</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -757,16 +779,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -934,16 +946,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1111,16 +1113,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1288,16 +1280,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
-  <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -571,14 +571,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <cols>
-    <col min="1" max="1" width="50.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="60.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,7 +662,7 @@
         <v>Reserve Bank of India (RBI) formulates monetary policy.</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>YES | 4/9/2026, 11:25:45 pm</v>
       </c>
     </row>
     <row r="4">

--- a/questions.xlsx
+++ b/questions.xlsx
@@ -413,16 +413,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -512,16 +502,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,16 +591,6 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -710,16 +680,6 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -809,16 +769,6 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -908,16 +858,6 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1007,16 +947,6 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1106,16 +1036,6 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1205,16 +1125,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1304,16 +1214,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1403,16 +1303,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1502,16 +1392,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1601,16 +1481,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1701,14 +1571,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
+    <col min="1" max="1" width="60.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1760,7 +1630,7 @@
         <v>The 42nd Amendment Act (1976) introduced extensive changes across the Preamble, Fundamental Duties, and DPSP, earning the title Mini-Constitution.</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>YES | 5/9/2026, 12:37:10 am</v>
       </c>
     </row>
     <row r="3">
@@ -1799,16 +1669,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1898,16 +1758,6 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H3"/>
-  <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
